--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/observations-summary.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="21">
   <si>
     <t>Profile</t>
   </si>
@@ -47,25 +47,34 @@
     <t>Method</t>
   </si>
   <si>
+    <t>at-prenudge-bloodglucose-observation</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE Observation Blood Glucose (only in mg/dL)</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>LOINC#1556-0</t>
+  </si>
+  <si>
+    <t>dateTime, Period, Timing, instant</t>
+  </si>
+  <si>
+    <t>integer</t>
+  </si>
+  <si>
+    <t>optional</t>
+  </si>
+  <si>
     <t>at-prenudge-stepcount-observation</t>
   </si>
   <si>
     <t>AT PreNUDGE Observation Step Count</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>LOINC#41950-7</t>
-  </si>
-  <si>
-    <t>dateTime, Period, Timing, instant</t>
-  </si>
-  <si>
-    <t>Quantity, CodeableConcept, string, boolean, integer, Range, Ratio, SampledData, time, dateTime, Period</t>
-  </si>
-  <si>
-    <t>optional</t>
   </si>
 </sst>
 </file>
@@ -199,7 +208,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -272,6 +281,41 @@
         <v>13</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K3" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/observations-summary.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="30">
   <si>
     <t>Profile</t>
   </si>
@@ -62,7 +62,7 @@
     <t>dateTime, Period, Timing, instant</t>
   </si>
   <si>
-    <t>integer</t>
+    <t>Quantityĵ</t>
   </si>
   <si>
     <t>optional</t>
@@ -75,6 +75,33 @@
   </si>
   <si>
     <t>LOINC#41950-7</t>
+  </si>
+  <si>
+    <t>at-prenudge-whoqol-bref-score-observation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> AT PreNUDGE Observation WHOQOL-BREF Score</t>
+  </si>
+  <si>
+    <t>SNOMED CT#405152002</t>
+  </si>
+  <si>
+    <t>SNOMED CT#60132005</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>SNOMED CT#19388002</t>
+  </si>
+  <si>
+    <t>SNOMED CT#60224009</t>
+  </si>
+  <si>
+    <t>SNOMED CT#272151006</t>
+  </si>
+  <si>
+    <t>SNOMED CT#276339004</t>
   </si>
 </sst>
 </file>
@@ -208,7 +235,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -316,6 +343,216 @@
         <v>13</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K4" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="F5" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="I5" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J5" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K5" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H6" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="I6" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J6" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K6" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H7" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="I7" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J7" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K7" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K8" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="F9" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H9" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="I9" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J9" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K9" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/observations-summary.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/observations-summary.xlsx
@@ -80,7 +80,7 @@
     <t>at-prenudge-whoqol-bref-score-observation</t>
   </si>
   <si>
-    <t xml:space="preserve"> AT PreNUDGE Observation WHOQOL-BREF Score</t>
+    <t>AT PreNUDGE Observation WHOQOL-BREF Score</t>
   </si>
   <si>
     <t>SNOMED CT#405152002</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/observations-summary.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="29">
   <si>
     <t>Profile</t>
   </si>
@@ -59,10 +59,10 @@
     <t>LOINC#1556-0</t>
   </si>
   <si>
-    <t>dateTime, Period, Timing, instant</t>
-  </si>
-  <si>
-    <t>Quantityĵ</t>
+    <t>dateTime</t>
+  </si>
+  <si>
+    <t>Quantity</t>
   </si>
   <si>
     <t>optional</t>
@@ -87,9 +87,6 @@
   </si>
   <si>
     <t>SNOMED CT#60132005</t>
-  </si>
-  <si>
-    <t>Quantity</t>
   </si>
   <si>
     <t>SNOMED CT#19388002</t>
@@ -401,7 +398,7 @@
         <v>13</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>17</v>
@@ -427,7 +424,7 @@
         <v>13</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s" s="2">
         <v>13</v>
@@ -436,7 +433,7 @@
         <v>13</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I6" t="s" s="2">
         <v>17</v>
@@ -462,7 +459,7 @@
         <v>13</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>13</v>
@@ -471,7 +468,7 @@
         <v>13</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>17</v>
@@ -497,7 +494,7 @@
         <v>13</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>13</v>
@@ -506,7 +503,7 @@
         <v>13</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>17</v>
@@ -532,7 +529,7 @@
         <v>13</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>13</v>
@@ -541,7 +538,7 @@
         <v>13</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>17</v>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/observations-summary.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="31">
   <si>
     <t>Profile</t>
   </si>
@@ -66,6 +66,12 @@
   </si>
   <si>
     <t>optional</t>
+  </si>
+  <si>
+    <t>SNOMED CT#309602000</t>
+  </si>
+  <si>
+    <t>CodeableConcept</t>
   </si>
   <si>
     <t>at-prenudge-stepcount-observation</t>
@@ -232,7 +238,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -307,28 +313,28 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s" s="2">
         <v>18</v>
       </c>
-      <c r="B3" t="s" s="2">
+      <c r="F3" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H3" t="s" s="2">
         <v>19</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="F3" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G3" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="H3" t="s" s="2">
-        <v>16</v>
       </c>
       <c r="I3" t="s" s="2">
         <v>17</v>
@@ -342,19 +348,19 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="B4" t="s" s="2">
+      <c r="C4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s" s="2">
         <v>22</v>
-      </c>
-      <c r="C4" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E4" t="s" s="2">
-        <v>23</v>
       </c>
       <c r="F4" t="s" s="2">
         <v>13</v>
@@ -363,7 +369,7 @@
         <v>15</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I4" t="s" s="2">
         <v>17</v>
@@ -377,10 +383,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s" s="2">
         <v>13</v>
@@ -389,16 +395,16 @@
         <v>13</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>17</v>
@@ -415,7 +421,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s" s="2">
         <v>13</v>
@@ -424,7 +430,7 @@
         <v>13</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s" s="2">
         <v>13</v>
@@ -450,7 +456,7 @@
         <v>13</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s" s="2">
         <v>13</v>
@@ -459,7 +465,7 @@
         <v>13</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>13</v>
@@ -485,7 +491,7 @@
         <v>13</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s" s="2">
         <v>13</v>
@@ -494,7 +500,7 @@
         <v>13</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>13</v>
@@ -520,7 +526,7 @@
         <v>13</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s" s="2">
         <v>13</v>
@@ -529,7 +535,7 @@
         <v>13</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>13</v>
@@ -547,6 +553,41 @@
         <v>13</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="F10" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G10" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H10" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I10" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J10" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K10" t="s" s="2">
         <v>13</v>
       </c>
     </row>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/observations-summary.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/observations-summary.xlsx
@@ -56,7 +56,7 @@
     <t/>
   </si>
   <si>
-    <t>LOINC#1556-0</t>
+    <t>LOINC#41653-7</t>
   </si>
   <si>
     <t>dateTime</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/observations-summary.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="37">
   <si>
     <t>Profile</t>
   </si>
@@ -72,6 +72,24 @@
   </si>
   <si>
     <t>CodeableConcept</t>
+  </si>
+  <si>
+    <t>at-prenudge-sleep-duration-observation</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE Observation Sleep Duration</t>
+  </si>
+  <si>
+    <t>LOINC#93832-4</t>
+  </si>
+  <si>
+    <t>at-prenudge-sleep-quality-observation</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE Observation Sleep Quality</t>
+  </si>
+  <si>
+    <t>LOINC#61987-4</t>
   </si>
   <si>
     <t>at-prenudge-stepcount-observation</t>
@@ -238,7 +256,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -404,7 +422,7 @@
         <v>15</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>17</v>
@@ -418,10 +436,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s" s="2">
         <v>13</v>
@@ -430,13 +448,13 @@
         <v>13</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F6" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>16</v>
@@ -453,10 +471,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s" s="2">
         <v>13</v>
@@ -465,16 +483,16 @@
         <v>13</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>17</v>
@@ -491,7 +509,7 @@
         <v>13</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s" s="2">
         <v>13</v>
@@ -500,7 +518,7 @@
         <v>13</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>13</v>
@@ -526,7 +544,7 @@
         <v>13</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s" s="2">
         <v>13</v>
@@ -535,7 +553,7 @@
         <v>13</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>13</v>
@@ -561,7 +579,7 @@
         <v>13</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s" s="2">
         <v>13</v>
@@ -570,24 +588,94 @@
         <v>13</v>
       </c>
       <c r="E10" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="F10" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G10" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H10" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I10" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J10" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K10" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>30</v>
       </c>
-      <c r="F10" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G10" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H10" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I10" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="J10" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K10" t="s" s="2">
+      <c r="C11" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="F11" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G11" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H11" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I11" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J11" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K11" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E12" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="F12" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J12" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K12" t="s" s="2">
         <v>13</v>
       </c>
     </row>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/observations-summary.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="40">
   <si>
     <t>Profile</t>
   </si>
@@ -72,6 +72,15 @@
   </si>
   <si>
     <t>CodeableConcept</t>
+  </si>
+  <si>
+    <t>at-prenudge-education-observation</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE Observation Highest Completed Education</t>
+  </si>
+  <si>
+    <t>LOINC#82589-3</t>
   </si>
   <si>
     <t>at-prenudge-sleep-duration-observation</t>
@@ -256,7 +265,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -387,7 +396,7 @@
         <v>15</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I4" t="s" s="2">
         <v>17</v>
@@ -422,7 +431,7 @@
         <v>15</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>17</v>
@@ -457,7 +466,7 @@
         <v>15</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I6" t="s" s="2">
         <v>17</v>
@@ -492,7 +501,7 @@
         <v>15</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>17</v>
@@ -506,10 +515,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s" s="2">
         <v>13</v>
@@ -518,16 +527,16 @@
         <v>13</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>17</v>
@@ -544,7 +553,7 @@
         <v>13</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s" s="2">
         <v>13</v>
@@ -553,7 +562,7 @@
         <v>13</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>13</v>
@@ -579,7 +588,7 @@
         <v>13</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s" s="2">
         <v>13</v>
@@ -588,7 +597,7 @@
         <v>13</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>13</v>
@@ -614,7 +623,7 @@
         <v>13</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s" s="2">
         <v>13</v>
@@ -623,7 +632,7 @@
         <v>13</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F11" t="s" s="2">
         <v>13</v>
@@ -649,7 +658,7 @@
         <v>13</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s" s="2">
         <v>13</v>
@@ -658,7 +667,7 @@
         <v>13</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F12" t="s" s="2">
         <v>13</v>
@@ -676,6 +685,41 @@
         <v>13</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="F13" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G13" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H13" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I13" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J13" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K13" t="s" s="2">
         <v>13</v>
       </c>
     </row>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/observations-summary.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="46">
   <si>
     <t>Profile</t>
   </si>
@@ -132,6 +132,24 @@
   </si>
   <si>
     <t>SNOMED CT#276339004</t>
+  </si>
+  <si>
+    <t>at-prenudge-work-soc-score-observation</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE Observation Work-SoC Category Score</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE Workability Codes#work-soc-category-score</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE Workability Codes#work-soc-comprehensibility</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE Workability Codes#work-soc-manageability</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE Workability Codes#work-soc-meaningfulness</t>
   </si>
 </sst>
 </file>
@@ -265,7 +283,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -723,6 +741,146 @@
         <v>13</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E14" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="F14" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="H14" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="I14" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J14" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K14" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E15" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="F15" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J15" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K15" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E16" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="F16" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J16" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K16" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="C17" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D17" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E17" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="F17" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K17" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/observations-summary.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="56">
   <si>
     <t>Profile</t>
   </si>
@@ -72,6 +72,36 @@
   </si>
   <si>
     <t>CodeableConcept</t>
+  </si>
+  <si>
+    <t>at-prenudge-bmi-observation</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE Observation Body Mass Index</t>
+  </si>
+  <si>
+    <t>Observation Category Codes#vital-signs</t>
+  </si>
+  <si>
+    <t>LOINC#39156-5</t>
+  </si>
+  <si>
+    <t>at-prenudge-bodyheight-observation</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE Observation Body Height</t>
+  </si>
+  <si>
+    <t>LOINC#8302-2</t>
+  </si>
+  <si>
+    <t>at-prenudge-bodyweight-observation</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE Observation Body Weight</t>
+  </si>
+  <si>
+    <t>LOINC#29463-7</t>
   </si>
   <si>
     <t>at-prenudge-education-observation</t>
@@ -283,7 +313,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -399,13 +429,13 @@
         <v>21</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s" s="2">
         <v>13</v>
@@ -414,7 +444,7 @@
         <v>15</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I4" t="s" s="2">
         <v>17</v>
@@ -428,19 +458,19 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5" t="s" s="2">
         <v>13</v>
@@ -463,19 +493,19 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F6" t="s" s="2">
         <v>13</v>
@@ -484,7 +514,7 @@
         <v>15</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I6" t="s" s="2">
         <v>17</v>
@@ -498,10 +528,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s" s="2">
         <v>13</v>
@@ -510,7 +540,7 @@
         <v>13</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>13</v>
@@ -519,7 +549,7 @@
         <v>15</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>17</v>
@@ -533,10 +563,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s" s="2">
         <v>13</v>
@@ -545,7 +575,7 @@
         <v>13</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>13</v>
@@ -554,7 +584,7 @@
         <v>15</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>17</v>
@@ -568,10 +598,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s" s="2">
         <v>13</v>
@@ -580,16 +610,16 @@
         <v>13</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>17</v>
@@ -603,10 +633,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s" s="2">
         <v>13</v>
@@ -615,13 +645,13 @@
         <v>13</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>16</v>
@@ -638,10 +668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s" s="2">
         <v>13</v>
@@ -650,16 +680,16 @@
         <v>13</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="F11" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>17</v>
@@ -676,7 +706,7 @@
         <v>13</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s" s="2">
         <v>13</v>
@@ -685,7 +715,7 @@
         <v>13</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F12" t="s" s="2">
         <v>13</v>
@@ -711,7 +741,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s" s="2">
         <v>13</v>
@@ -720,7 +750,7 @@
         <v>13</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F13" t="s" s="2">
         <v>13</v>
@@ -743,10 +773,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s" s="2">
         <v>13</v>
@@ -755,16 +785,16 @@
         <v>13</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F14" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>17</v>
@@ -781,7 +811,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s" s="2">
         <v>13</v>
@@ -790,7 +820,7 @@
         <v>13</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F15" t="s" s="2">
         <v>13</v>
@@ -816,7 +846,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C16" t="s" s="2">
         <v>13</v>
@@ -825,7 +855,7 @@
         <v>13</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F16" t="s" s="2">
         <v>13</v>
@@ -848,10 +878,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s" s="2">
         <v>13</v>
@@ -860,16 +890,16 @@
         <v>13</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F17" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>17</v>
@@ -878,6 +908,111 @@
         <v>13</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D18" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E18" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="F18" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J18" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K18" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D19" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E19" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="F19" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K19" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="F20" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K20" t="s" s="2">
         <v>13</v>
       </c>
     </row>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/observations-summary.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="65">
   <si>
     <t>Profile</t>
   </si>
@@ -111,6 +111,33 @@
   </si>
   <si>
     <t>LOINC#82589-3</t>
+  </si>
+  <si>
+    <t>at-prenudge-nutrition-fruitportions-observation</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE Observation Nutrition Fruit Portions</t>
+  </si>
+  <si>
+    <t>LOINC#89765-5</t>
+  </si>
+  <si>
+    <t>at-prenudge-nutrition-sugarsalty-observation</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE Observation Nutrition Sugar Salty Frequency</t>
+  </si>
+  <si>
+    <t>SNOMED CT#364395008</t>
+  </si>
+  <si>
+    <t>at-prenudge-nutrition-vegetableportions-observation</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE Observation Nutrition Vegetable Portions</t>
+  </si>
+  <si>
+    <t>LOINC#89764-8</t>
   </si>
   <si>
     <t>at-prenudge-sleep-duration-observation</t>
@@ -313,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -689,7 +716,7 @@
         <v>15</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>17</v>
@@ -703,10 +730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s" s="2">
         <v>13</v>
@@ -715,16 +742,16 @@
         <v>13</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F12" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>17</v>
@@ -738,10 +765,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s" s="2">
         <v>13</v>
@@ -750,13 +777,13 @@
         <v>13</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F13" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>16</v>
@@ -773,10 +800,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C14" t="s" s="2">
         <v>13</v>
@@ -785,16 +812,16 @@
         <v>13</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F14" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>17</v>
@@ -811,7 +838,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C15" t="s" s="2">
         <v>13</v>
@@ -820,7 +847,7 @@
         <v>13</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F15" t="s" s="2">
         <v>13</v>
@@ -846,7 +873,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C16" t="s" s="2">
         <v>13</v>
@@ -855,7 +882,7 @@
         <v>13</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F16" t="s" s="2">
         <v>13</v>
@@ -878,10 +905,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C17" t="s" s="2">
         <v>13</v>
@@ -890,16 +917,16 @@
         <v>13</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F17" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>17</v>
@@ -916,7 +943,7 @@
         <v>13</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s" s="2">
         <v>13</v>
@@ -925,7 +952,7 @@
         <v>13</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F18" t="s" s="2">
         <v>13</v>
@@ -951,7 +978,7 @@
         <v>13</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C19" t="s" s="2">
         <v>13</v>
@@ -960,7 +987,7 @@
         <v>13</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>13</v>
@@ -983,10 +1010,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C20" t="s" s="2">
         <v>13</v>
@@ -995,16 +1022,16 @@
         <v>13</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>17</v>
@@ -1013,6 +1040,111 @@
         <v>13</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D21" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E21" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="F21" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D22" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E22" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="F22" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K22" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D23" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E23" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="F23" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J23" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K23" t="s" s="2">
         <v>13</v>
       </c>
     </row>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/observations-summary.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="78">
   <si>
     <t>Profile</t>
   </si>
@@ -113,6 +113,15 @@
     <t>LOINC#82589-3</t>
   </si>
   <si>
+    <t>at-prenudge-muscle-strengthening-observation</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE Observation Muscle Strengthening Sessions</t>
+  </si>
+  <si>
+    <t>LOINC#82291-6</t>
+  </si>
+  <si>
     <t>at-prenudge-nutrition-fruitportions-observation</t>
   </si>
   <si>
@@ -138,6 +147,36 @@
   </si>
   <si>
     <t>LOINC#89764-8</t>
+  </si>
+  <si>
+    <t>at-prenudge-physical-activity-minutes-observation</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE Observation Physical Activity Minutes</t>
+  </si>
+  <si>
+    <t>LOINC#101691-4</t>
+  </si>
+  <si>
+    <t>Quantity, CodeableConcept, string, boolean, integer, Range, Ratio, SampledData, time, dateTime, Period</t>
+  </si>
+  <si>
+    <t>LOINC#77592-4</t>
+  </si>
+  <si>
+    <t>LOINC#77593-2</t>
+  </si>
+  <si>
+    <t>SNOMED CT#246501002</t>
+  </si>
+  <si>
+    <t>at-prenudge-sitting-hours-observation</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE Observation Sitting Hours</t>
+  </si>
+  <si>
+    <t>LOINC#87705-0</t>
   </si>
   <si>
     <t>at-prenudge-sleep-duration-observation</t>
@@ -340,7 +379,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -646,7 +685,7 @@
         <v>15</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>17</v>
@@ -681,7 +720,7 @@
         <v>15</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>17</v>
@@ -751,7 +790,7 @@
         <v>15</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>17</v>
@@ -765,25 +804,25 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s" s="2">
         <v>49</v>
       </c>
-      <c r="C13" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D13" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E13" t="s" s="2">
-        <v>50</v>
-      </c>
       <c r="F13" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>16</v>
@@ -800,10 +839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s" s="2">
         <v>13</v>
@@ -812,16 +851,16 @@
         <v>13</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F14" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>17</v>
@@ -838,7 +877,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s" s="2">
         <v>13</v>
@@ -847,7 +886,7 @@
         <v>13</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="F15" t="s" s="2">
         <v>13</v>
@@ -873,7 +912,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s" s="2">
         <v>13</v>
@@ -882,7 +921,7 @@
         <v>13</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F16" t="s" s="2">
         <v>13</v>
@@ -891,7 +930,7 @@
         <v>13</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>17</v>
@@ -905,10 +944,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C17" t="s" s="2">
         <v>13</v>
@@ -917,13 +956,13 @@
         <v>13</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F17" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>16</v>
@@ -940,10 +979,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C18" t="s" s="2">
         <v>13</v>
@@ -958,7 +997,7 @@
         <v>13</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>16</v>
@@ -975,10 +1014,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C19" t="s" s="2">
         <v>13</v>
@@ -987,16 +1026,16 @@
         <v>13</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>17</v>
@@ -1010,10 +1049,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C20" t="s" s="2">
         <v>13</v>
@@ -1022,7 +1061,7 @@
         <v>13</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>13</v>
@@ -1031,7 +1070,7 @@
         <v>15</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>17</v>
@@ -1045,10 +1084,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C21" t="s" s="2">
         <v>13</v>
@@ -1057,16 +1096,16 @@
         <v>13</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F21" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>17</v>
@@ -1083,7 +1122,7 @@
         <v>13</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C22" t="s" s="2">
         <v>13</v>
@@ -1092,7 +1131,7 @@
         <v>13</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F22" t="s" s="2">
         <v>13</v>
@@ -1118,7 +1157,7 @@
         <v>13</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C23" t="s" s="2">
         <v>13</v>
@@ -1127,7 +1166,7 @@
         <v>13</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F23" t="s" s="2">
         <v>13</v>
@@ -1145,6 +1184,251 @@
         <v>13</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D24" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E24" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="F24" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D25" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E25" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="F25" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D26" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E26" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="F26" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K26" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D27" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F27" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K27" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D28" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F28" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="F29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K30" t="s" s="2">
         <v>13</v>
       </c>
     </row>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/observations-summary.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="101">
   <si>
     <t>Profile</t>
   </si>
@@ -170,6 +170,66 @@
     <t>SNOMED CT#246501002</t>
   </si>
   <si>
+    <t>at-prenudge-pss10-score-observation</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE Observation PSS-10 Score</t>
+  </si>
+  <si>
+    <t>LOINC#106860-0</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE PSS Instrument Codes#pss10-q1</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE PSS Instrument Codes#pss10-q2</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE PSS Instrument Codes#pss10-q3</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE PSS Instrument Codes#pss10-q4</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE PSS Instrument Codes#pss10-q5</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE PSS Instrument Codes#pss10-q6</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE PSS Instrument Codes#pss10-q7</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE PSS Instrument Codes#pss10-q8</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE PSS Instrument Codes#pss10-q9</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE PSS Instrument Codes#pss10-q10</t>
+  </si>
+  <si>
+    <t>at-prenudge-pss4-score-observation</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE Observation PSS-4 Score</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE PSS Instrument Codes#pss4</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE PSS Instrument Codes#pss4-q1</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE PSS Instrument Codes#pss4-q2</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE PSS Instrument Codes#pss4-q3</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE PSS Instrument Codes#pss4-q4</t>
+  </si>
+  <si>
     <t>at-prenudge-sitting-hours-observation</t>
   </si>
   <si>
@@ -204,6 +264,15 @@
   </si>
   <si>
     <t>LOINC#41950-7</t>
+  </si>
+  <si>
+    <t>at-prenudge-whooley-observation</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE Observation Whooley Depression Screening</t>
+  </si>
+  <si>
+    <t>LOINC#73832-8</t>
   </si>
   <si>
     <t>at-prenudge-whoqol-bref-score-observation</t>
@@ -379,7 +448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -979,28 +1048,28 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D18" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E18" t="s" s="2">
         <v>55</v>
       </c>
-      <c r="B18" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="C18" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D18" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E18" t="s" s="2">
-        <v>57</v>
-      </c>
       <c r="F18" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>17</v>
@@ -1014,10 +1083,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C19" t="s" s="2">
         <v>13</v>
@@ -1026,13 +1095,13 @@
         <v>13</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>19</v>
@@ -1049,10 +1118,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="C20" t="s" s="2">
         <v>13</v>
@@ -1061,16 +1130,16 @@
         <v>13</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>17</v>
@@ -1084,10 +1153,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="C21" t="s" s="2">
         <v>13</v>
@@ -1096,16 +1165,16 @@
         <v>13</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="F21" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>17</v>
@@ -1122,7 +1191,7 @@
         <v>13</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="C22" t="s" s="2">
         <v>13</v>
@@ -1131,7 +1200,7 @@
         <v>13</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F22" t="s" s="2">
         <v>13</v>
@@ -1140,7 +1209,7 @@
         <v>13</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>17</v>
@@ -1157,7 +1226,7 @@
         <v>13</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="C23" t="s" s="2">
         <v>13</v>
@@ -1166,7 +1235,7 @@
         <v>13</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F23" t="s" s="2">
         <v>13</v>
@@ -1175,7 +1244,7 @@
         <v>13</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>17</v>
@@ -1192,7 +1261,7 @@
         <v>13</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="C24" t="s" s="2">
         <v>13</v>
@@ -1201,7 +1270,7 @@
         <v>13</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F24" t="s" s="2">
         <v>13</v>
@@ -1210,7 +1279,7 @@
         <v>13</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>17</v>
@@ -1227,7 +1296,7 @@
         <v>13</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="C25" t="s" s="2">
         <v>13</v>
@@ -1236,7 +1305,7 @@
         <v>13</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>13</v>
@@ -1245,7 +1314,7 @@
         <v>13</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>17</v>
@@ -1262,7 +1331,7 @@
         <v>13</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="C26" t="s" s="2">
         <v>13</v>
@@ -1271,7 +1340,7 @@
         <v>13</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>13</v>
@@ -1280,7 +1349,7 @@
         <v>13</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>17</v>
@@ -1294,10 +1363,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="C27" t="s" s="2">
         <v>13</v>
@@ -1306,16 +1375,16 @@
         <v>13</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="F27" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>17</v>
@@ -1329,10 +1398,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C28" t="s" s="2">
         <v>13</v>
@@ -1341,13 +1410,13 @@
         <v>13</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F28" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>16</v>
@@ -1367,7 +1436,7 @@
         <v>13</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C29" t="s" s="2">
         <v>13</v>
@@ -1376,7 +1445,7 @@
         <v>13</v>
       </c>
       <c r="E29" t="s" s="2">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="F29" t="s" s="2">
         <v>13</v>
@@ -1385,7 +1454,7 @@
         <v>13</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>17</v>
@@ -1402,33 +1471,628 @@
         <v>13</v>
       </c>
       <c r="B30" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E30" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="F30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D31" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E31" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="F31" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D32" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E32" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="F32" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="C30" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D30" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E30" t="s" s="2">
+      <c r="C33" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D33" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F33" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D34" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E34" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="F30" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G30" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H30" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I30" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="J30" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K30" t="s" s="2">
+      <c r="F34" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D35" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="F35" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D36" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="F36" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C37" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D37" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E37" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="F37" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D38" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E38" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="F38" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D39" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E39" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="F39" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D40" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E40" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="F40" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D41" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E41" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="F41" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D42" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E42" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="F42" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D43" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E43" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="F43" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D44" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E44" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="F44" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D45" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E45" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="F45" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="C46" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D46" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E46" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="F46" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D47" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E47" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F47" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K47" t="s" s="2">
         <v>13</v>
       </c>
     </row>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/observations-summary.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/observations-summary.xlsx
@@ -128,7 +128,7 @@
     <t>AT PreNUDGE Observation Nutrition Fruit Portions</t>
   </si>
   <si>
-    <t>LOINC#89765-5</t>
+    <t>LOINC#80457-5</t>
   </si>
   <si>
     <t>at-prenudge-nutrition-sugarsalty-observation</t>
@@ -146,7 +146,7 @@
     <t>AT PreNUDGE Observation Nutrition Vegetable Portions</t>
   </si>
   <si>
-    <t>LOINC#89764-8</t>
+    <t>LOINC#80459-1</t>
   </si>
   <si>
     <t>at-prenudge-physical-activity-minutes-observation</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/observations-summary.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="102">
   <si>
     <t>Profile</t>
   </si>
@@ -165,6 +165,9 @@
   </si>
   <si>
     <t>LOINC#77593-2</t>
+  </si>
+  <si>
+    <t>SNOMED CT#68130003</t>
   </si>
   <si>
     <t>SNOMED CT#246501002</t>
@@ -448,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -999,7 +1002,7 @@
         <v>13</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>17</v>
@@ -1013,28 +1016,28 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="C17" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D17" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E17" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="B17" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="C17" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D17" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E17" t="s" s="2">
-        <v>54</v>
-      </c>
       <c r="F17" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>17</v>
@@ -1048,10 +1051,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C18" t="s" s="2">
         <v>13</v>
@@ -1066,10 +1069,10 @@
         <v>13</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>17</v>
@@ -1086,7 +1089,7 @@
         <v>13</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C19" t="s" s="2">
         <v>13</v>
@@ -1121,7 +1124,7 @@
         <v>13</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C20" t="s" s="2">
         <v>13</v>
@@ -1156,7 +1159,7 @@
         <v>13</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C21" t="s" s="2">
         <v>13</v>
@@ -1191,7 +1194,7 @@
         <v>13</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C22" t="s" s="2">
         <v>13</v>
@@ -1226,7 +1229,7 @@
         <v>13</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C23" t="s" s="2">
         <v>13</v>
@@ -1261,7 +1264,7 @@
         <v>13</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C24" t="s" s="2">
         <v>13</v>
@@ -1296,7 +1299,7 @@
         <v>13</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C25" t="s" s="2">
         <v>13</v>
@@ -1331,7 +1334,7 @@
         <v>13</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C26" t="s" s="2">
         <v>13</v>
@@ -1366,7 +1369,7 @@
         <v>13</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C27" t="s" s="2">
         <v>13</v>
@@ -1398,28 +1401,28 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D28" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E28" t="s" s="2">
         <v>65</v>
       </c>
-      <c r="B28" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="C28" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D28" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E28" t="s" s="2">
-        <v>67</v>
-      </c>
       <c r="F28" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>17</v>
@@ -1433,10 +1436,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C29" t="s" s="2">
         <v>13</v>
@@ -1451,10 +1454,10 @@
         <v>13</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>17</v>
@@ -1471,7 +1474,7 @@
         <v>13</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C30" t="s" s="2">
         <v>13</v>
@@ -1506,7 +1509,7 @@
         <v>13</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C31" t="s" s="2">
         <v>13</v>
@@ -1541,7 +1544,7 @@
         <v>13</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C32" t="s" s="2">
         <v>13</v>
@@ -1573,28 +1576,28 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D33" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E33" t="s" s="2">
         <v>72</v>
       </c>
-      <c r="B33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D33" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E33" t="s" s="2">
-        <v>74</v>
-      </c>
       <c r="F33" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>17</v>
@@ -1608,19 +1611,19 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D34" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E34" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D34" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E34" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>13</v>
@@ -1643,19 +1646,19 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D35" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E35" t="s" s="2">
         <v>78</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D35" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E35" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="F35" t="s" s="2">
         <v>13</v>
@@ -1664,7 +1667,7 @@
         <v>15</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>17</v>
@@ -1678,19 +1681,19 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D36" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E36" t="s" s="2">
         <v>81</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D36" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E36" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>13</v>
@@ -1699,7 +1702,7 @@
         <v>15</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>17</v>
@@ -1713,19 +1716,19 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="C37" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D37" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E37" t="s" s="2">
         <v>84</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="C37" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D37" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E37" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>13</v>
@@ -1734,7 +1737,7 @@
         <v>15</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>17</v>
@@ -1748,19 +1751,19 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D38" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E38" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C38" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D38" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E38" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>13</v>
@@ -1769,7 +1772,7 @@
         <v>15</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>17</v>
@@ -1783,10 +1786,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C39" t="s" s="2">
         <v>13</v>
@@ -1801,10 +1804,10 @@
         <v>13</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>17</v>
@@ -1821,7 +1824,7 @@
         <v>13</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C40" t="s" s="2">
         <v>13</v>
@@ -1856,7 +1859,7 @@
         <v>13</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C41" t="s" s="2">
         <v>13</v>
@@ -1891,7 +1894,7 @@
         <v>13</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C42" t="s" s="2">
         <v>13</v>
@@ -1926,7 +1929,7 @@
         <v>13</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C43" t="s" s="2">
         <v>13</v>
@@ -1958,28 +1961,28 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D44" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E44" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="B44" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D44" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E44" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="F44" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>17</v>
@@ -1993,10 +1996,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C45" t="s" s="2">
         <v>13</v>
@@ -2011,10 +2014,10 @@
         <v>13</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>17</v>
@@ -2031,7 +2034,7 @@
         <v>13</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C46" t="s" s="2">
         <v>13</v>
@@ -2066,7 +2069,7 @@
         <v>13</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C47" t="s" s="2">
         <v>13</v>
@@ -2093,6 +2096,41 @@
         <v>13</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D48" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E48" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="F48" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K48" t="s" s="2">
         <v>13</v>
       </c>
     </row>
